--- a/data_extactor/batch_10_fa/batch_0079_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0079_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe Creative Cloud software | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk AutoCAD | Autodesk Revit | Fluke Corporation FlukeView Forms | IBM Lotus 1-2-3 | IBM Lotus Notes | Linux | Megger PowerDB | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Trimble SketchUp Pro</t>
+          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk AutoCAD | Autodesk Revit | Fluke Corporation FlukeView Forms | IBM Lotus 1-2-3 | IBM Lotus Notes | Linux | Megger PowerDB | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Trimble SketchUp Pro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | مانیتورینگ | درک مطلب | سخن گفتن | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | درک مطلب | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | کامپیوتر و الکترونیک | ریاضیات | امنیت و ایمنی عمومی | مکانیک | طراحی | زبان انگلیسی | مخابرات | آموزش و تربیت | خدمات مشتریان و پرسنلی | تولید و فرآوری | حمل و نقل | فیزیک</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مکانیک | طراحی | زبان انگلیسی | مخابرات | آموزش و پرورش | خدمات مشتری و شخصی | تولید و فرآوری | حمل و نقل | فیزیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | بینایی نزدیک | حساسیت به مشکل | زبردستی دستی | تشخیص رنگ بصری | زبردستی انگشتان | درک شفاهی | ترتیب‌دهی اطلاعات | دقت کنترل | هماهنگی چند عضو | انعطاف‌پذیری بدنی | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | بینایی دور | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک کتبی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | مهارت دستی | تشخیص رنگ بصری | مهارت انگشتان | درک شفاهی | ترتیب‌دهی اطلاعات | دقت کنترل | هماهنگی چند عضو | انعطاف‌پذیری دامنه حرکت | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | بینایی دور | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب بدنی | داخل ساختمان، بدون کنترل محیطی | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | داخل ساختمان، دارای کنترل محیطی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌زدگی‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | آزادی در تصمیم‌گیری | پیامد اشتباه | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | آزادی در تصمیم‌گیری | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان ساختار، سطوح، تجهیزات پروازی و سیستم‌های هواپیما | تکنسین‌های اویونیک | فناوران و تکنسین‌های کالیبراسیون | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | فناوران و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | فناوران و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکنندگان تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | دستیاران برق‌کار | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های نورپردازی | کارکنان تعمیر و نگهداری، عمومی | فناوران و تکنسین‌های مهندسی مکانیک | سازندگان و نصب‌کنندگان ماشین‌آلات صنعتی | تکنسین‌های رباتیک</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | دستیاران--برق‌کاران | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های نورپردازی | کارگران نگهداری و تعمیرات عمومی | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان نصب ماشین‌آلات | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Circuit evaluation software | Computerized maintenance management system CMMS | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | Programmable logic controller PLC software | Rockwell RSLogix | SAP Maintenance</t>
+          <t>Autodesk AutoCAD | Circuit evaluation software | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | Rockwell RSLogix | SAP Maintenance</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | مانیتورینگ | یادگیری فعال | نگارش</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مکانیک | تولید و فرآوری | خدمات مشتریان و پرسنلی | ریاضیات | امور اداری و مدیریت | مهندسی و فناوری | زبان انگلیسی | طراحی | آموزش و تربیت</t>
+          <t>رایانه و الکترونیک | مکانیک | تولید و فرآوری | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره | مهندسی و فناوری | زبان انگلیسی | طراحی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مشکل | ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی | استدلال قیاسی | ثبات دست و بازو | زبردستی دستی | زبردستی انگشتان | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم فضایی | تشخیص رنگ بصری | بیان شفاهی | درک کتبی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | بینایی دور | دقت کنترل | توجه انتخابی | اصالت | روان بودن ایده‌ها | بیان کتبی</t>
+          <t>حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی | استدلال قیاسی | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم | تشخیص رنگ بصری | بیان شفاهی | درک کتبی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | بینایی دور | دقت کنترل | توجه انتخابی | اصالت | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | داخل ساختمان، دارای کنترل محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای ایستادن | نزدیکی فیزیکی | پیامد اشتباه</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای ایستادن | نزدیکی فیزیکی | پیامد خطا</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>فناوران و تکنسین‌های مهندسی هوافضا و عملیات | مونتاژکنندگان ساختار، سطوح، تجهیزات پروازی و سیستم‌های هواپیما | تکنسین‌های اویونیک | فناوران و تکنسین‌های کالیبراسیون | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مهندسان برق | فناوران و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | فناوران و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکنندگان تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | مکانیک‌های ماشین‌آلات صنعتی | فناوران و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکنندگان تجهیزات پزشکی | تکنسین‌های رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Fluke Corporation FlukeView Forms | Megger PowerDB | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | OMICRON Test Universe | نرم‌افزار مانیتورینگ و کنترل داده SCADA | نرم‌افزار مرورگر وب</t>
+          <t>Autodesk AutoCAD | Fluke Corporation FlukeView Forms | Megger PowerDB | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | OMICRON Test Universe | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال | مانیتورینگ</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | مهندسی و فناوری | امنیت و ایمنی عمومی | زبان انگلیسی | کامپیوتر و الکترونیک | طراحی | فیزیک | ساختمان و ساخت‌وساز | آموزش و تربیت</t>
+          <t>مکانیک | ریاضیات | مهندسی و فناوری | ایمنی و امنیت عمومی | زبان انگلیسی | رایانه و الکترونیک | طراحی | فیزیک | ساختمان و ساخت‌وساز | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | درک شفاهی | حساسیت به مشکل | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | زبردستی انگشتان | دقت کنترل | تشخیص رنگ بصری | زبردستی دستی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان کتبی | بینایی دور | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | مهارت انگشتان | دقت کنترل | تشخیص رنگ بصری | مهارت دستی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان کتبی | بینایی دور | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | پیامد اشتباه | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | ایمیل | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت تکرار وظایف مشابه | فشار زمانی | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | داخل ساختمان، بدون کنترل محیطی | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض شرایط نوری بسیار روشن یا نامناسب | داخل ساختمان، دارای کنترل محیطی | صرف زمان برای ایستادن | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض ارتفاعات | فضای باز، زیر سقف | آزادی در تصمیم‌گیری | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت تکرار وظایف یکسان | فشار زمانی | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض ارتفاعات بالا | فضای باز، زیر سقف | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان ساختار، سطوح، تجهیزات پروازی و سیستم‌های هواپیما | فناوران و تکنسین‌های کالیبراسیون | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مهندسان برق | نصب‌کنندگان و تعمیرکنندگان خطوط انتقال نیروی برق | فناوران و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | برق‌کاران | مونتاژکنندگان تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های نورپردازی | توزیع‌کنندگان و دیسپچرهای برق | تکنسین‌های رباتیک | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مهندسان برق | نصابان و تعمیرکاران خطوط انتقال نیروی برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | برق‌کاران | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های نورپردازی | توزیع‌کنندگان و دیسپچرهای برق | تکنسین‌های رباتیک | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیک | کامپیوتر و الکترونیک | خدمات مشتریان و پرسنلی | ریاضیات | زبان انگلیسی | مهندسی و فناوری | آموزش و تربیت</t>
+          <t>مکانیک | رایانه و الکترونیک | خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | زبردستی انگشتان | بینایی نزدیک | تشخیص رنگ بصری | حساسیت به مشکل | استدلال قیاسی | تجسم فضایی | انعطاف‌پذیری بدنی | استدلال استقرایی | درک شفاهی | زبردستی دستی | توجه انتخابی | دقت کنترل | بیان شفاهی | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | انعطاف‌پذیری دسته‌بندی | درک کتبی | قدرت تنه | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تقسیم توجه | انعطاف‌پذیری بستار | روان بودن ایده‌ها</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | تشخیص رنگ بصری | حساسیت به مسئله | استدلال قیاسی | تجسم | انعطاف‌پذیری دامنه حرکت | استدلال استقرایی | درک شفاهی | مهارت دستی | توجه انتخابی | دقت کنترل | بیان شفاهی | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | انعطاف‌پذیری دسته‌بندی | درک کتبی | قدرت تنه | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تقسیم توجه | انعطاف‌پذیری بستار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | داخل ساختمان، بدون کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب بدنی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | صرف زمان برای خم کردن یا چرخاندن بدن | ارتباط با دیگران</t>
+          <t>اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | محیط داخلی، بدون کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | صرف زمان برای خم کردن یا چرخاندن بدن | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان ساختار، سطوح، تجهیزات پروازی و سیستم‌های هواپیما | نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های مهندسی خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های اویونیک | فناوران و تکنسین‌های کالیبراسیون | تعمیرکنندگان کامپیوتر، خودپرداز و ماشین‌های اداری | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | فناوران و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکنندگان تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | مونتاژکنندگان موتور و سایر ماشین‌آلات | تکنسین‌های نورپردازی | نصب‌کنندگان و تعمیرکنندگان تجهیزات رادیویی، سلولار و دکل | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | نصب‌کنندگان و تعمیرکنندگان تجهیزات مخابراتی، به جز نصب‌کنندگان خطوط</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های مهندسی خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | مونتاژکاران موتور و سایر ماشین‌آلات | تکنسین‌های نورپردازی | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Audio calibration software | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word</t>
+          <t>نرم‌افزار کالیبراسیون صدا | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | خدمات مشتریان و پرسنلی | مخابرات | مکانیک | زبان انگلیسی | مهندسی و فناوری | امور اداری و مدیریت | ساختمان و ساخت‌وساز</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مخابرات | مکانیک | زبان انگلیسی | مهندسی و فناوری | مدیریت و اداره | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>زبردستی انگشتان | بینایی نزدیک | تجسم فضایی | حساسیت به مشکل | استدلال قیاسی | ترتیب‌دهی اطلاعات | زبردستی دستی | بینایی دور | تشخیص رنگ بصری | درک شفاهی | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | دقت کنترل | توجه انتخابی | انعطاف‌پذیری بستار | درک کتبی</t>
+          <t>مهارت انگشتان | بینایی نزدیک | تجسم | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | مهارت دستی | بینایی دور | تشخیص رنگ بصری | درک شفاهی | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | دقت کنترل | توجه انتخابی | انعطاف‌پذیری بستار | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | فشار زمانی | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>مکالمات تلفنی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فشار زمانی | فضای باز، در معرض تمام شرایط آب و هوایی | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌های صدا و تصویر | تکنسین‌های اویونیک | تکنسین‌های پخش برنامه | فناوران و تکنسین‌های کالیبراسیون | تعمیرکنندگان دوربین و تجهیزات عکاسی | تعمیرکنندگان کامپیوتر، خودپرداز و ماشین‌های اداری | فناوران و تکنسین‌های مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکنندگان تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌های نورپردازی | آپاراتچی‌های سینما | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | نصب‌کنندگان و تعمیرکنندگان تجهیزات رادیویی، سلولار و دکل | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | متخصصان مهندسی مخابرات | نصب‌کنندگان و تعمیرکنندگان تجهیزات مخابراتی، به جز نصب‌کنندگان خطوط | نصب‌کنندگان و تعمیرکنندگان خطوط مخابراتی</t>
+          <t>تکنسین‌های صوتی و تصویری | تکنسین‌های هوانوردی | تکنسین‌های پخش | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌های نورپردازی | آپاراتچی‌های سینما | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | مانیتورینگ</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | کامپیوتر و الکترونیک | خدمات مشتریان و پرسنلی | مخابرات | ساختمان و ساخت‌وساز | مهندسی و فناوری | زبان انگلیسی | مکانیک | آموزش و تربیت</t>
+          <t>ایمنی و امنیت عمومی | رایانه و الکترونیک | خدمات مشتری و شخصی | مخابرات | ساختمان و ساخت‌وساز | مهندسی و فناوری | زبان انگلیسی | مکانیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مشکل | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | زبردستی دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال استقرایی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بدنی | هماهنگی چند عضو | زبردستی انگشتان | بینایی دور | دقت کنترل | سرعت ادراکی | بیان کتبی | درک کتبی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | مهارت دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال استقرایی | تجسم | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | مهارت انگشتان | بینایی دور | دقت کنترل | سرعت ادراکی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم | داخل ساختمان، بدون کنترل محیطی | پیامدهای کاری و نتایج سایر کارکنان | داخل ساختمان، دارای کنترل محیطی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء, ابزارها یا کنترل‌ها | پیامد اشتباه | نامه‌ها و یادداشت‌های کتبی | نزدیکی فیزیکی</t>
+          <t>مکالمات تلفنی | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، بدون کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامد خطا | نامه‌ها و یادداشت‌های کتبی | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های اویونیک | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | فناوران و تکنسین‌های مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | برق‌کاران | مونتاژکنندگان تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | مهندسان پیشگیری و حفاظت از حریق | تکنسین‌های نورپردازی | کارکنان تعمیر و نگهداری، عمومی | تسترهای نفوذ | توزیع‌کنندگان و دیسپچرهای برق | نصب‌کنندگان و تعمیرکنندگان تجهیزات رادیویی، سلولار و دکل | متخصصان مدیریت امنیت | نصب‌کنندگان و تعمیرکنندگان تجهیزات مخابراتی، به جز نصب‌کنندگان خطوط | نصب‌کنندگان و تعمیرکنندگان خطوط مخابراتی</t>
+          <t>نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های هوانوردی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | برق‌کاران | مونتاژکاران تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | مهندسان پیشگیری و حفاظت از آتش‌سوزی | تکنسین‌های نورپردازی | کارگران نگهداری و تعمیرات عمومی | کارشناسان آزمون نفوذ | توزیع‌کنندگان و دیسپچرهای برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | متخصصان مدیریت امنیت | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Access Software AIRPAX | CaseBank SpotLight | Computerized aircraft log manager CALM | DatcoMedia EBis | Disassembler software | Engine analysis software | Maintenance information databases | Maintenance planning software | Maintenance record software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Mxi Technologies Maintenix | Operational Data Store ODS software | Pentagon 2000SQL | نرم‌افزار SAP | Supply system software | Technical Data Management System TDMS | Technical manual database software | Tracware AeroTrac | نرم‌افزار مرورگر وب</t>
+          <t>Access Software AIRPAX | CaseBank SpotLight | Computerized aircraft log manager CALM | DatcoMedia EBis | نرم‌افزار جداسازی | Engine analysis software | Maintenance information databases | Maintenance planning software | نرم‌افزار ثبت تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Mxi Technologies Maintenix | نرم‌افزار ذخیره‌سازی داده‌های عملیاتی ODS | Pentagon 2000SQL | نرم‌افزار SAP | Supply system software | سیستم مدیریت داده‌های فنی TDMS | Technical manual database software | Tracware AeroTrac | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | مانیتورینگ | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | امنیت و ایمنی عمومی | مهندسی و فناوری | زبان انگلیسی | حمل و نقل | آموزش و تربیت | ریاضیات | فیزیک | کامپیوتر و الکترونیک | طراحی</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | زبان انگلیسی | حمل و نقل | آموزش و پرورش | ریاضیات | فیزیک | رایانه و الکترونیک | طراحی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مشکل | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | زبردستی دستی | زبردستی انگشتان | دقت کنترل | استدلال قیاسی | استدلال استقرایی | هماهنگی چند عضو | انعطاف‌پذیری بستار | ثبات دست و بازو | بیان شفاهی | درک شفاهی | حساسیت شنوایی | تجسم فضایی | تشخیص رنگ بصری | بینایی دور | سرعت ادراکی | قدرت تنه | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بدنی | وضوح گفتار | توجه شنیداری | تشخیص گفتار | درک عمق | قدرت ایستا | زمان عکس‌العمل | جهت‌گیری پاسخ | سرعت بستار</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | مهارت دستی | مهارت انگشتان | دقت کنترل | استدلال قیاسی | استدلال استقرایی | هماهنگی چند عضو | انعطاف‌پذیری بستار | ثبات دست و بازو | بیان شفاهی | درک شفاهی | حساسیت شنوایی | تجسم | تشخیص رنگ بصری | بینایی دور | سرعت ادراکی | قدرت تنه | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری دامنه حرکت | وضوح گفتار | توجه شنیداری | تشخیص گفتار | درک عمق | قدرت ایستا | زمان عکس‌العمل | جهت‌گیری پاسخ | سرعت بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | داخل ساختمان, بدون کنترل محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب بدنی | ایمیل | اهمیت تکرار وظایف مشابه | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم کردن یا چرخاندن بدن</t>
+          <t>قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | محیط داخلی، بدون کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | ایمیل | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>فناوران و تکنسین‌های مهندسی هوافضا و عملیات | مهندسان هوافضا | خدمه خدمات هواپیما | مونتاژکنندگان ساختار، سطوح، تجهیزات پروازی و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های اویونیک | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | فناوران و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | تعمیرکنندگان ماشین‌آلات | مکانیک‌های تجهیزات سنگین سیار، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | تعمیرکنندگان واگن‌های ریلی | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | متصدیان خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | تعمیرکنندگان واگن‌های ریلی | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Accounts receivable software | Appointment scheduling software | AutoZone ALLDATA | Automotive and Accounting Software by R*KOM Invoice Writer | Collision damage estimation software | Collision damage measurement software | Equipment management information software | Materials management software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Windows | Microsoft Word | Paint mixing and matching software | Swan River Estimiser Pro</t>
+          <t>نرم‌افزار حساب‌های دریافتنی | نرم‌افزار زمان‌بندی قرار ملاقات | AutoZone ALLDATA | Automotive and Accounting Software by R*KOM Invoice Writer | Collision damage estimation software | Collision damage measurement software | Equipment management information software | Materials management software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Windows | Microsoft Word | Paint mixing and matching software | Swan River Estimiser Pro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | مانیتورینگ | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و پرسنلی | تولید و فرآوری | ریاضیات</t>
+          <t>مکانیک | خدمات مشتری و شخصی | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | زبردستی دستی | تجسم فضایی | درک شفاهی | حساسیت به مشکل | ترتیب‌دهی اطلاعات | زبردستی انگشتان | بینایی نزدیک | تشخیص رنگ بصری | تشخیص گفتار | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | توجه شنیداری | انعطاف‌پذیری بدنی | قدرت تنه | قدرت ایستا | انعطاف‌پذیری بستار | درک کتبی | وضوح گفتار</t>
+          <t>ثبات دست و بازو | مهارت دستی | تجسم | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت انگشتان | بینایی نزدیک | تشخیص رنگ بصری | تشخیص گفتار | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | توجه شنیداری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | انعطاف‌پذیری بستار | درک کتبی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای ایستادن | آزادی در تصمیم‌گیری | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند ماسک تنفسی، کمربند ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | داخل ساختمان، بدون کنترل محیطی | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | سطح رقابت | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب بدنی</t>
+          <t>قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای ایستادن | آزادی در تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | سطح رقابت | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان ساختار، سطوح، تجهیزات پروازی و سیستم‌های هواپیما | نصب‌کنندگان و تعمیرکنندگان شیشه خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان موتور و سایر ماشین‌آلات | پرداخت‌کنندگان مبلمان | کارگران سنباده‌زنی و پولیش‌کاری، دستی | مکانیک‌های ماشین‌آلات صنعتی | تعمیرکنندگان ماشین‌آلات | مکانیک‌های تجهیزات سنگین سیار، به جز موتورها | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | مکانیک‌های موتورسیکلت | تعمیرکنندگان واگن‌های ریلی | کارگران ورق‌کار | سازندگان و مونتاژکنندگان سازه‌های فلزی | سازندگان تایر | تعمیرکنندگان و تعویض‌کنندگان تایر | رویه‌کوبان مبل</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نصب‌کنندگان و تعمیرکنندگان شیشه خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران موتور و سایر ماشین‌آلات | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | مکانیک‌های موتورسیکلت | تعمیرکنندگان واگن‌های ریلی | کارگران ورق‌کاری | سازندگان و مونتاژکاران فلزات سازه‌ای | تایر سازان | تعمیرکنندگان و تعویض‌کنندگان لاستیک | روکوبان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Estimating software | Microsoft Windows | Recordkeeping software | Workday software</t>
+          <t>Estimating software | Microsoft Windows | نرم‌افزار ثبت سوابق | نرم‌افزار Workday</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -969,22 +969,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | مکانیک | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | قدرت ایستا | هماهنگی چند عضو | زبردستی دستی | تشخیص گفتار | انعطاف‌پذیری بدنی | دقت کنترل | زبردستی انگشتان | ثبات دست و بازو | تجسم فضایی | استدلال قیاسی | حساسیت به مشکل | بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات</t>
+          <t>بینایی نزدیک | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | تجسم | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | ارتباط با دیگران | فشار زمانی | داخل ساختمان، بدون کنترل محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | فضای باز، زیر سقف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌زدگی‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | قرار گرفتن در معرض شرایط نوری بسیار روشن یا نامناسب | صرف زمان برای انجام حرکات تکراری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | ارتباط با دیگران | فشار زمانی | محیط داخلی، بدون کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | فضای باز، زیر سقف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان ساختار، سطوح، تجهیزات پروازی و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌ها و مکانیک‌های خدمات خودرو | تمیزکنندگان وسایل نقلیه و تجهیزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | پرداخت‌کنندگان مبلمان | شیشه‌گران، قالب‌ریزان، خم‌کنندگان و پرداخت‌کنندگان شیشه | شیشه‌بران و نصابان شیشه ساختمان | کارگران سنباده‌زنی و پولیش‌کاری, دستی | تعمیرکنندگان لوازم خانگی | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | تعمیرکنندگان درب‌های مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزئینات | تعمیرکنندگان واگن‌های ریلی | سازندگان و مونتاژکنندگان سازه‌های فلزی | سازندگان تایر | تعمیرکنندگان و تعویض‌کنندگان تایر</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌ها و مکانیک‌های خدمات خودرو | تمیزکنندگان وسایل نقلیه و تجهیزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | پرداخت‌کاران مبلمان | شیشه‌گران، قالب‌سازان، خم‌کاران و پرداخت‌کاران شیشه | شیشه‌بران | کارگران سنگ‌زنی و پرداخت دستی | تعمیرکاران لوازم خانگی | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | تعمیرکاران درب‌های مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزیین | تعمیرکنندگان واگن‌های ریلی | سازندگان و مونتاژکاران فلزات سازه‌ای | تایر سازان | تعمیرکنندگان و تعویض‌کنندگان لاستیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Alliance Automotive Shop Controller | Amcom AUTOS2000 | Apple Safari | AutoZone ALLDATA | Blue Streak Electronics Buell Diagnostic | CODA Engine Analysis System | نرم‌افزار پایگاه داده | Estimating software | Genisys Fast Fixes | Hunter WinAlign | IBM Notes | Mainsaver Asset Management | Microsoft Edge | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | Mitchell Manager Invoicing System | Mitchell OnDemand5 Manager | Mozilla Firefox | Nexiq Tech HDS Suite for Palm | Online service manual database software | Recordkeeping software | نرم‌افزار SAP | SPX/OTC Genisys ConnecTech PC | Scheduling software | Scott Systems MaxxTraxx Pro | Snap-On ShopKey | Technical manual database software | Vehicle management software | Work order management software | YouTube</t>
+          <t>Alliance Automotive Shop Controller | Amcom AUTOS2000 | Apple Safari | AutoZone ALLDATA | Blue Streak Electronics Buell Diagnostic | CODA Engine Analysis System | نرم‌افزار پایگاه داده | Estimating software | Genisys Fast Fixes | Hunter WinAlign | IBM Notes | Mainsaver Asset Management | Microsoft Edge | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | Mitchell Manager Invoicing System | Mitchell OnDemand5 Manager | Mozilla Firefox | Nexiq Tech HDS Suite for Palm | Online service manual database software | نرم‌افزار ثبت سوابق | نرم‌افزار SAP | SPX/OTC Genisys ConnecTech PC | نرم‌افزار زمان‌بندی | Scott Systems MaxxTraxx Pro | Snap-On ShopKey | Technical manual database software | نرم‌افزار مدیریت وسیله نقلیه | Work order management software | YouTube</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | گوش دادن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و پرسنلی | کامپیوتر و الکترونیک | مهندسی و فناوری</t>
+          <t>مکانیک | خدمات مشتری و شخصی | رایانه و الکترونیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | زبردستی دستی | بینایی نزدیک | زبردستی انگشتان | حساسیت به مشکل | استدلال استقرایی | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری بدنی | تجسم فضایی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | هماهنگی چند عضو | بیان شفاهی | تقسیم توجه | توجه شنیداری | تشخیص رنگ بصری | قدرت تنه | جهت‌گیری پاسخ | انعطاف‌پذیری دسته‌بندی</t>
+          <t>استدلال قیاسی | مهارت دستی | بینایی نزدیک | مهارت انگشتان | حساسیت به مسئله | استدلال استقرایی | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری دامنه حرکت | تجسم | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | هماهنگی چند عضو | بیان شفاهی | تقسیم توجه | توجه شنیداری | تشخیص رنگ بصری | قدرت تنه | جهت‌گیری پاسخ | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | فشار زمانی | ارتباط با دیگران | قرار گرفتن در معرض شرایط خطرناک | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب بدنی | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌زدگی‌ها | مکالمات تلفنی | داخل ساختمان، بدون کنترل محیطی | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای انجام حرکات تکراری | پیامد اشتباه</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | فشار زمانی | ارتباط با دیگران | قرار گرفتن در معرض شرایط خطرناک | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | مکالمات تلفنی | محیط داخلی، بدون کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای انجام حرکات تکراری | پیامد خطا</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان ساختار، سطوح، تجهیزات پروازی و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌های مهندسی خودرو | مهندسان خودرو | تکنسین‌های اویونیک | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | تعمیرکنندگان ماشین‌آلات | مکانیک‌های تجهیزات سنگین سیار، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برقی فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | تعمیرکنندگان و تعویض‌کنندگان تایر</t>
+          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌های مهندسی خودرو | مهندسان خودرو | تکنسین‌های هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های موتورسیکلت | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | تعمیرکنندگان و تعویض‌کنندگان لاستیک</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0079_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0079_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت | درک مطلب | سخن گفتن | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | درک مطلب | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مکانیک | طراحی | زبان انگلیسی | مخابرات | آموزش و پرورش | خدمات مشتریان و خدمات فردی | تولید و فراوری | ترابری | فیزیک</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مکانیک | طراحی | زبان انگلیسی | مخابرات | آموزش و پرورش | خدمات مشتری و شخصی | تولید و فرآوری | حمل و نقل | فیزیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | حساسیت به مسئله | چابکی دستی | تشخیص رنگ | چابکی انگشتان | درک شفاهی | مرتب‌سازی اطلاعات | دقت کنترل | هماهنگی چند اندام | انعطاف‌پذیری بدنی | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | دید دور | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | بیان شفاهی | درک کتبی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | مهارت دستی | تشخیص رنگ بصری | مهارت انگشتان | درک شفاهی | ترتیب‌دهی اطلاعات | دقت کنترل | هماهنگی چند عضو | انعطاف‌پذیری دامنه حرکت | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | بینایی دور | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکار سازه، سطوح، مهار و سیستم‌های هواپیما | تکنسین اویونیک و الکترونیک هوانوردی | تکنسین کالیبراسیون | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترلی | تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | کاردان فنی مهندسی برق و الکترونیک | مونتاژکار تجهیزات الکتریکی و الکترونیکی | تعمیرکار تجهیزات برقی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | تکنسین الکترومکانیک و مکاترونیک | مونتاژکار تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مهندس الکترونیک (غیر از رایانه) | کمک‌برق‌کار | مکانیک ماشین‌آلات صنعتی | تکنسین سیستم‌های روشنایی | تعمیرکار و مسئول نگهداری عمومی ساختمان و تجهیزات | تکنسین مهندسی مکانیک | مهندس مکانیک صنعتی و نصاب تجهیزات صنعتی (میلرایت) | تکنسین رباتیک</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مهندسان الکترونیک، به‌جز کامپیوتر | کمک‌برق‌کاران | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های نورپردازی | کارگران عمومی تعمیرات و نگهداری تاسیسات | کارشناسان و تکنسین‌های مهندسی مکانیک | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مکانیک | تولید و فراوری | خدمات مشتریان و خدمات فردی | ریاضیات | مدیریت و امور اداری | مهندسی و فناوری | زبان انگلیسی | طراحی | آموزش و پرورش</t>
+          <t>رایانه و الکترونیک | مکانیک | تولید و فرآوری | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره | مهندسی و فناوری | زبان انگلیسی | طراحی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | درک شفاهی | استدلال قیاسی | ثبات دست و بازو | چابکی دستی | چابکی انگشتان | انعطاف‌پذیری در ادراک الگوها | سرعت ادراک | تجسم فضایی | تشخیص رنگ | بیان شفاهی | درک کتبی | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | دید دور | دقت کنترل | توجه انتخابی | ابتکار و خلاقیت | روان‌بودن جریان اندیشه | بیان کتبی</t>
+          <t>حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی | استدلال قیاسی | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم | تشخیص رنگ بصری | بیان شفاهی | درک کتبی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | بینایی دور | دقت کنترل | توجه انتخابی | اصالت | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کاردان فنی هوافضا و عملیات پرواز | مونتاژکار سازه، سطوح، مهار و سیستم‌های هواپیما | تکنسین اویونیک و الکترونیک هوانوردی | تکنسین کالیبراسیون | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترلی | تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | مهندس برق | کاردان فنی مهندسی برق و الکترونیک | مونتاژکار تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | تکنسین الکترومکانیک و مکاترونیک | مونتاژکار تجهیزات الکترومکانیکی | مهندس الکترونیک (غیر از رایانه) | مکانیک ماشین‌آلات صنعتی | تکنسین مهندسی مکانیک | مهندس مکانیک | مهندس مکاترونیک | تعمیرکار تجهیزات پزشکی | تکنسین رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز کامپیوتر | مکانیک‌های ماشین‌آلات صنعتی | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | شنیدن فعال | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | مهندسی و فناوری | ایمنی و امنیت عمومی | زبان انگلیسی | رایانه و الکترونیک | طراحی | فیزیک | ساختمان و سازه | آموزش و پرورش</t>
+          <t>مکانیک | ریاضیات | مهندسی و فناوری | ایمنی و امنیت عمومی | زبان انگلیسی | رایانه و الکترونیک | طراحی | فیزیک | ساختمان و ساخت‌وساز | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | چابکی انگشتان | دقت کنترل | تشخیص رنگ | چابکی دستی | سرعت ادراک | انعطاف‌پذیری در ادراک الگوها | استدلال استقرایی | استدلال قیاسی | بیان کتبی | دید دور | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | مهارت انگشتان | دقت کنترل | تشخیص رنگ بصری | مهارت دستی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان کتبی | بینایی دور | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکار سازه، سطوح، مهار و سیستم‌های هواپیما | تکنسین کالیبراسیون | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترلی | تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | مهندس برق | سیم‌بان و تعمیرکار خطوط انتقال و توزیع برق | کاردان فنی مهندسی برق و الکترونیک | مونتاژکار تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات برقی و الکترونیکی صنعتی و تجاری | برق‌کار | مونتاژکار تجهیزات الکترومکانیکی | مهندس الکترونیک (غیر از رایانه) | تکنسین انرژی زمین‌گرمایی | تکنسین نیروگاه‌های برق‌آبی | مکانیک ماشین‌آلات صنعتی | تکنسین سیستم‌های روشنایی | دیسپاچر و توزیع‌کننده انرژی برق | تکنسین رباتیک | مهندس مکانیک تأسیسات و اپراتور دیگ‌های بخار</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان فنی کالیبراسیون | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مهندسان برق | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | برق‌کاران | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز کامپیوتر | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های نورپردازی | دیسپچرها و توزیع‌کنندگان شبکه برق | تکنسین‌های رباتیک | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیک | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | ریاضیات | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش</t>
+          <t>مکانیک | رایانه و الکترونیک | خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | دید نزدیک | تشخیص رنگ | حساسیت به مسئله | استدلال قیاسی | تجسم فضایی | انعطاف‌پذیری بدنی | استدلال استقرایی | درک شفاهی | چابکی دستی | توجه انتخابی | دقت کنترل | بیان شفاهی | مرتب‌سازی اطلاعات | هماهنگی چند اندام | انعطاف‌پذیری طبقه‌بندی | درک کتبی | قدرت تنه | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تقسیم توجه | انعطاف‌پذیری در ادراک الگوها | روان‌بودن جریان اندیشه</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | تشخیص رنگ بصری | حساسیت به مسئله | استدلال قیاسی | تجسم | انعطاف‌پذیری دامنه حرکت | استدلال استقرایی | درک شفاهی | مهارت دستی | توجه انتخابی | دقت کنترل | بیان شفاهی | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | انعطاف‌پذیری دسته‌بندی | درک کتبی | قدرت تنه | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تقسیم توجه | انعطاف‌پذیری بستار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مونتاژکار سازه، سطوح، مهار و سیستم‌های هواپیما | نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین مهندسی خودرو | مکانیک و تکنسین خدمات خودرو | تکنسین اویونیک و الکترونیک هوانوردی | تکنسین کالیبراسیون | تعمیرکار رایانه، خودپرداز و ماشین‌های اداری | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترلی | تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | کاردان فنی مهندسی برق و الکترونیک | مونتاژکار تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات برقی و الکترونیکی صنعتی و تجاری | مونتاژکار تجهیزات الکترومکانیکی | مهندس الکترونیک (غیر از رایانه) | مونتاژکار موتور و ماشین‌آلات | تکنسین سیستم‌های روشنایی | نصاب و تعمیرکار تجهیزات رادیویی، دکل و تلفن همراه | نصاب سیستم‌های اعلام سرقت و حریق | نصاب و تعمیرکار تجهیزات مخابراتی (به‌جز نصابان خطوط)</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های مهندسی خودرو | مکانیک و تکنسین خدمات خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز کامپیوتر | مونتاژکاران موتور و سایر ماشین‌آلات | تکنسین‌های نورپردازی | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | نصاب سیستم‌های اعلام سرقت و حریق | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,22 +731,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار کالیبراسیون صدا | نرم‌افزار سامانه موقعیت‌یاب جهانی GPS | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Word</t>
+          <t>نرم‌افزار کالیبراسیون صدا | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Word</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | تفکر انتقادی</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مخابرات | مکانیک | زبان انگلیسی | مهندسی و فناوری | مدیریت و امور اداری | ساختمان و سازه</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مخابرات | مکانیک | زبان انگلیسی | مهندسی و فناوری | مدیریت و اداره | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | دید نزدیک | تجسم فضایی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | چابکی دستی | دید دور | تشخیص رنگ | درک شفاهی | ثبات دست و بازو | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | دقت کنترل | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | درک کتبی</t>
+          <t>مهارت انگشتان | بینایی نزدیک | تجسم | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | مهارت دستی | بینایی دور | تشخیص رنگ بصری | درک شفاهی | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | دقت کنترل | توجه انتخابی | انعطاف‌پذیری بستار | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین صوت و تصویر | تکنسین اویونیک و الکترونیک هوانوردی | تکنسین پخش و فرستنده‌های رادیو و تلویزیونی | تکنسین کالیبراسیون | تعمیرکار دوربین و تجهیزات عکاسی | تعمیرکار رایانه، خودپرداز و ماشین‌های اداری | کاردان فنی مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات برقی و الکترونیکی صنعتی و تجاری | مونتاژکار تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مهندس الکترونیک (غیر از رایانه) | تکنسین سیستم‌های روشنایی | اپراتور آپارات و اکران فیلم سینمایی | متخصص تجهیزات شناسایی فرکانس رادیویی RFID | نصاب و تعمیرکار تجهیزات رادیویی، دکل و تلفن همراه | نصاب سیستم‌های اعلام سرقت و حریق | کارشناس مهندسی مخابرات | نصاب و تعمیرکار تجهیزات مخابراتی (به‌جز نصابان خطوط) | سیم‌بان و نصاب خطوط مخابراتی</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌های پخش و اتاق فرمان | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مهندسان الکترونیک، به‌جز کامپیوتر | تکنسین‌های نورپردازی | آپاراتچی‌ها و تکنسین‌های نمایش فیلم | متخصصان سامانه‌های شناسایی با امواج رادیویی | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | نصاب سیستم‌های اعلام سرقت و حریق | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | نصابان و کابل‌کشان خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مخابرات | ساختمان و سازه | مهندسی و فناوری | زبان انگلیسی | مکانیک | آموزش و پرورش</t>
+          <t>ایمنی و امنیت عمومی | رایانه و الکترونیک | خدمات مشتری و شخصی | مخابرات | ساختمان و ساخت‌وساز | مهندسی و فناوری | زبان انگلیسی | مکانیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | دید نزدیک | استدلال قیاسی | چابکی دستی | ثبات دست و بازو | مرتب‌سازی اطلاعات | استدلال استقرایی | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بدنی | هماهنگی چند اندام | چابکی انگشتان | دید دور | دقت کنترل | سرعت ادراک | بیان کتبی | درک کتبی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | مهارت دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال استقرایی | تجسم | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | مهارت انگشتان | بینایی دور | دقت کنترل | سرعت ادراکی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین اویونیک و الکترونیک هوانوردی | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترلی | کاردان فنی مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات برقی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | برق‌کار | مونتاژکار تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مهندس الکترونیک (غیر از رایانه) | مهندس حفاظت و پیشگیری از حریق | تکنسین سیستم‌های روشنایی | تعمیرکار و مسئول نگهداری عمومی ساختمان و تجهیزات | کارشناس آزمون نفوذپذیری | دیسپاچر و توزیع‌کننده انرژی برق | نصاب و تعمیرکار تجهیزات رادیویی، دکل و تلفن همراه | کارشناس مدیریت امنیت اطلاعات و شبکه | نصاب و تعمیرکار تجهیزات مخابراتی (به‌جز نصابان خطوط) | سیم‌بان و نصاب خطوط مخابراتی</t>
+          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های اویونیک و الکترونیک پرواز | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | برق‌کاران | مونتاژکاران تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان پیشگیری و حفاظت از حریق | تکنسین‌های نورپردازی | کارگران عمومی تعمیرات و نگهداری تاسیسات | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | دیسپچرها و توزیع‌کنندگان شبکه برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | کارشناسان مدیریت حراست و امنیت فیزیکی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | نصابان و کابل‌کشان خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | زبان انگلیسی | ترابری | آموزش و پرورش | ریاضیات | فیزیک | رایانه و الکترونیک | طراحی</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | زبان انگلیسی | حمل و نقل | آموزش و پرورش | ریاضیات | فیزیک | رایانه و الکترونیک | طراحی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات | چابکی دستی | چابکی انگشتان | دقت کنترل | استدلال قیاسی | استدلال استقرایی | هماهنگی چند اندام | انعطاف‌پذیری در ادراک الگوها | ثبات دست و بازو | بیان شفاهی | درک شفاهی | حساسیت شنوایی | تجسم فضایی | تشخیص رنگ | دید دور | سرعت ادراک | قدرت تنه | بیان کتبی | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی | انعطاف‌پذیری بدنی | وضوح گفتار | توجه شنیداری | تشخیص گفتار | درک عمق | قدرت ایستایی | زمان واکنش | جهت‌یابی پاسخ | سرعت بستن الگو</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | مهارت دستی | مهارت انگشتان | دقت کنترل | استدلال قیاسی | استدلال استقرایی | هماهنگی چند عضو | انعطاف‌پذیری بستار | ثبات دست و بازو | بیان شفاهی | درک شفاهی | حساسیت شنوایی | تجسم | تشخیص رنگ بصری | بینایی دور | سرعت ادراکی | قدرت تنه | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری دامنه حرکت | وضوح گفتار | توجه شنیداری | تشخیص گفتار | درک عمق | قدرت ایستا | زمان عکس‌العمل | جهت‌گیری پاسخ | سرعت بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کاردان فنی هوافضا و عملیات پرواز | مهندس هوافضا | خدمه خدمات زمینی هواپیما | مونتاژکار سازه، سطوح، مهار و سیستم‌های هواپیما | مکانیک و تکنسین خدمات خودرو | تکنسین اویونیک و الکترونیک هوانوردی | مکانیک خودروهای سنگین و دیزل | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترلی | تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات برقی و الکترونیکی صنعتی و تجاری | تکنسین الکترومکانیک و مکاترونیک | مونتاژکار موتور و ماشین‌آلات | مکانیک ماشین‌آلات صنعتی | تعمیرکار و کارگر نگهداری ماشین‌آلات | مکانیک ماشین‌آلات سنگین متحرک (به‌جز موتور) | تعمیرکار قایق موتوری | تعمیرکار واگن و خودروهای ریلی | مهندس موتورخانه شناور | مهندس مکانیک تأسیسات و اپراتور دیگ‌های بخار</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مکانیک و تکنسین خدمات خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | تعمیرکار واگن قطار | مهندسان فنی کشتی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | تولید و فراوری | ریاضیات</t>
+          <t>مکانیک | خدمات مشتری و شخصی | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | تجسم فضایی | درک شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | چابکی انگشتان | دید نزدیک | تشخیص رنگ | تشخیص گفتار | هماهنگی چند اندام | دقت کنترل | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | بیان شفاهی | توجه شنیداری | انعطاف‌پذیری بدنی | قدرت تنه | قدرت ایستایی | انعطاف‌پذیری در ادراک الگوها | درک کتبی | وضوح گفتار</t>
+          <t>ثبات دست و بازو | مهارت دستی | تجسم | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت انگشتان | بینایی نزدیک | تشخیص رنگ بصری | تشخیص گفتار | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | توجه شنیداری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | انعطاف‌پذیری بستار | درک کتبی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکار سازه، سطوح، مهار و سیستم‌های هواپیما | نصاب و تعمیرکار شیشه خودرو | مکانیک و تکنسین خدمات خودرو | مکانیک خودروهای سنگین و دیزل | متصدی و اپراتور دستگاه‌های رنگ‌کاری و پوشش‌دهی | تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | مونتاژکار موتور و ماشین‌آلات | رنگ‌کار و پرداخت‌کننده مصنوعات چوبی | پرداخت‌کار و سنباده‌کار دستی سطوح | مکانیک ماشین‌آلات صنعتی | تعمیرکار و کارگر نگهداری ماشین‌آلات | مکانیک ماشین‌آلات سنگین متحرک (به‌جز موتور) | قالب‌ریز و مدل‌ساز (غیرفلزی و پلاستیک) | مکانیک موتورسیکلت | تعمیرکار واگن و خودروهای ریلی | ورق‌کار و سازنده قطعات فلزی | سازنده و مونتاژکار سازه‌های فلزی | سازنده لاستیک خودرو | آپاراتی و تعمیرکار لاستیک | رویه‌کوب و تودوزی‌کار خودرو و مبل</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصاب و تعمیرکار شیشه خودرو | مکانیک و تکنسین خدمات خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | مکانیک موتورسیکلت | تعمیرکار واگن قطار | کارگران ورق‌کاری فلزی | سازندگان و مونتاژکاران سازه‌های فلزی | سازندگان تایر | آپاراتی و پنچرگیر و تعویض‌کار لاستیک | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Workday | نرم‌افزار برآورد هزینه خسارت | نرم‌افزار ثبت اطلاعات و اسناد | نرم‌افزار Microsoft Windows</t>
+          <t>Estimating software | Microsoft Windows | نرم‌افزار ثبت سوابق | نرم‌افزار Workday</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مکانیک | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | قدرت ایستایی | هماهنگی چند اندام | چابکی دستی | تشخیص گفتار | انعطاف‌پذیری بدنی | دقت کنترل | چابکی انگشتان | ثبات دست و بازو | تجسم فضایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | تجسم | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکار سازه، سطوح، مهار و سیستم‌های هواپیما | صافکار و نقاش خودرو | مکانیک و تکنسین خدمات خودرو | متصدی شست‌وشوی خودرو و تجهیزات | متصدی و اپراتور دستگاه‌های رنگ‌کاری و پوشش‌دهی | تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | رنگ‌کار و پرداخت‌کننده مصنوعات چوبی | شیشه‌دم و فرم‌دهنده شیشه | شیشه‌بر و نصاب شیشه ساختمان | پرداخت‌کار و سنباده‌کار دستی سطوح | تعمیرکار لوازم خانگی | عایق‌کار کف، سقف و دیوار | عایق‌کار تأسیسات و سیستم‌های مکانیکی | تعمیرکار درب‌های اتوماتیک و مکانیکی | قالب‌ریز و مدل‌ساز (غیرفلزی و پلاستیک) | رنگ‌کار، نقاش و تزیین‌کننده قطعات | تعمیرکار واگن و خودروهای ریلی | سازنده و مونتاژکار سازه‌های فلزی | سازنده لاستیک خودرو | آپاراتی و تعمیرکار لاستیک</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | صافکار و نقاش خودرو | مکانیک و تکنسین خدمات خودرو | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | شیشه‌بران و نصابان شیشه | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تعمیرکاران لوازم خانگی | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | تعمیرکاران درب‌های مکانیکی و اتوماتیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تعمیرکار واگن قطار | سازندگان و مونتاژکاران سازه‌های فلزی | سازندگان تایر | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مهندسی و فناوری</t>
+          <t>مکانیک | خدمات مشتری و شخصی | رایانه و الکترونیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | چابکی دستی | دید نزدیک | چابکی انگشتان | حساسیت به مسئله | استدلال استقرایی | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری بدنی | تجسم فضایی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | انعطاف‌پذیری در ادراک الگوها | سرعت ادراک | توجه انتخابی | هماهنگی چند اندام | بیان شفاهی | تقسیم توجه | توجه شنیداری | تشخیص رنگ | قدرت تنه | جهت‌یابی پاسخ | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>استدلال قیاسی | مهارت دستی | بینایی نزدیک | مهارت انگشتان | حساسیت به مسئله | استدلال استقرایی | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری دامنه حرکت | تجسم | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | هماهنگی چند عضو | بیان شفاهی | تقسیم توجه | توجه شنیداری | تشخیص رنگ بصری | قدرت تنه | جهت‌گیری پاسخ | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکار سازه، سطوح، مهار و سیستم‌های هواپیما | صافکار و نقاش خودرو | تکنسین مهندسی خودرو | مهندس خودرو | تکنسین اویونیک و الکترونیک هوانوردی | مکانیک خودروهای سنگین و دیزل | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترلی | تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مونتاژکار موتور و ماشین‌آلات | مکانیک ماشین‌آلات صنعتی | تعمیرکار و کارگر نگهداری ماشین‌آلات | مکانیک ماشین‌آلات سنگین متحرک (به‌جز موتور) | تعمیرکار قایق موتوری | مکانیک موتورسیکلت | مکانیک ماشین‌آلات سبک و ادوات کشاورزی | تعمیرکار واگن و خودروهای ریلی | آپاراتی و تعمیرکار لاستیک</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | صافکار و نقاش خودرو | تکنسین‌های مهندسی خودرو | مهندسان خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
